--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T09:13:57+00:00</t>
+    <t>2023-06-15T09:14:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -240,13 +240,13 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>PractitionerRole.meta.extension:as-data-trace</t>
-  </si>
-  <si>
-    <t>as-data-trace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t>PractitionerRole.meta.extension:as-ext-data-trace</t>
+  </si>
+  <si>
+    <t>as-ext-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
 </t>
   </si>
   <si>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T09:14:52+00:00</t>
+    <t>2023-06-16T14:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1797,7 +1797,7 @@
     <t>Often practitioners have a dedicated line for each location (or service) that they work at, and need to be able to define separate contact details for each of these.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:code}
+    <t xml:space="preserve">profile:$this.resolve()}
 </t>
   </si>
   <si>
@@ -2310,7 +2310,7 @@
     <col min="25" max="25" width="168.7265625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="107.80859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="21.17578125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="21.8671875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="54.1171875" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-16T14:16:48+00:00</t>
+    <t>2023-07-03T12:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-03T12:37:47+00:00</t>
+    <t>2023-07-10T14:48:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4551" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4549" uniqueCount="600">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-10T14:48:30+00:00</t>
+    <t>2023-07-10T14:51:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -993,13 +993,10 @@
 </t>
   </si>
   <si>
-    <t>identifiant métier calculé à partir des identifiants techniques de l'exercice professionnel et la situation d'exercice.</t>
+    <t>identifiant métier calculé à partir des identifiants techniques de l'exercice professionnel et la situation d'exercice (Synonyme : idFonctionnel).</t>
   </si>
   <si>
     <t>Business Identifiers that are specific to a role/location.</t>
-  </si>
-  <si>
-    <t>Synonyme : idFonctionnel</t>
   </si>
   <si>
     <t>Often, specific identities are assigned for the agent.</t>
@@ -1091,13 +1088,13 @@
     <t>PractitionerRole.identifier.value</t>
   </si>
   <si>
-    <t>Identifiant technique de l'activité.</t>
+    <t>Identifiant technique de l'activité (Synonyme : idActivite).</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>Synonyme : idActivite</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1192,19 +1189,19 @@
     <t>PractitionerRole.period.start</t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Date de début de l’activité correspondant à la date d’installation en cabinet ou à la date d’embauche du salarié.</t>
-  </si>
-  <si>
-    <t>Synonyme : dateDebutActivite</t>
+    <t>[Donnée restreinte] : Date de début de l’activité correspondant à la date d’installation en cabinet ou à la date d’embauche du salarié (Synonyme : dateDebutActivite).</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
   </si>
   <si>
     <t>PractitionerRole.period.end</t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Date de fin de l’activité.</t>
-  </si>
-  <si>
-    <t>Synonyme : dateFinActivite</t>
+    <t>[Donnée restreinte] : Date de fin de l’activité (Synonyme : dateFinActivite).</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
   </si>
   <si>
     <t>PractitionerRole.practitioner</t>
@@ -1214,13 +1211,13 @@
 </t>
   </si>
   <si>
-    <t>Référence permettant de lier l’exercice professionnel et la situation d'exercice à un professionnel (Practitioner).</t>
+    <t>Référence permettant de lier l’exercice professionnel et la situation d'exercice à un professionnel (Practitioner). (Synonyme : idPP)</t>
   </si>
   <si>
     <t>Practitioner that is able to provide the defined services for the organization.</t>
   </si>
   <si>
-    <t>Synonyme : idPP</t>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
     <t>PractitionerRole.organization</t>
@@ -1230,13 +1227,10 @@
 </t>
   </si>
   <si>
-    <t>Référence vers l’EG ou EJ de rattachement de la situation d’exercice (Organization)</t>
+    <t>Référence vers l’EG ou EJ de rattachement de la situation d’exercice (Organization) (Synonyme : idNat_Struct)</t>
   </si>
   <si>
     <t>The organization where the Practitioner performs the roles associated.</t>
-  </si>
-  <si>
-    <t>Synonyme : idNat_Strcut</t>
   </si>
   <si>
     <t>PractitionerRole.code</t>
@@ -1294,10 +1288,7 @@
     <t>CategorieProfession</t>
   </si>
   <si>
-    <t>Catégorie professionnelle indiqant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant.</t>
-  </si>
-  <si>
-    <t>Synonyme : categorieProfessionnelle</t>
+    <t>Catégorie professionnelle indiqant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (Synonyme : categorieProfessionnelle).</t>
   </si>
   <si>
     <t>Liste des catégories professionnelles</t>
@@ -1312,10 +1303,7 @@
     <t>professionG15</t>
   </si>
   <si>
-    <t>Profession exercée ou future profession de l'étudiant.</t>
-  </si>
-  <si>
-    <t>Synonyme : professionSante</t>
+    <t>Profession exercée ou future profession de l'étudiant (Synonyme : professionSante).</t>
   </si>
   <si>
     <t>Liste des professions de santé  définies par le code de la santé publique</t>
@@ -1330,10 +1318,7 @@
     <t>professionR94</t>
   </si>
   <si>
-    <t>Profession du social.</t>
-  </si>
-  <si>
-    <t>Synonyme : professionSocial</t>
+    <t>Profession du social (Synonyme : professionSocial).</t>
   </si>
   <si>
     <t>Liste des professions du social</t>
@@ -1345,10 +1330,7 @@
     <t>professionR95</t>
   </si>
   <si>
-    <t>Profession à usage de titre professionnel.</t>
-  </si>
-  <si>
-    <t>Synonyme : usagerTitre</t>
+    <t>Profession à usage de titre professionnel (Synonyme : usagerTitre).</t>
   </si>
   <si>
     <t>Liste des professions à usage de titre professionnel</t>
@@ -1360,10 +1342,7 @@
     <t>professionR291</t>
   </si>
   <si>
-    <t>professionnel non membre d'une profession réglementée.</t>
-  </si>
-  <si>
-    <t>Synonyme : autreProfession</t>
+    <t>professionnel non membre d'une profession réglementée (Synonyme : autreProfession).</t>
   </si>
   <si>
     <t>Liste de professionnels non membres d'une profession réglementée</t>
@@ -1375,10 +1354,7 @@
     <t>genreActivite</t>
   </si>
   <si>
-    <t>Le genre identifiant une activité qui nécessite l’application de règles de gestion spécifiques.</t>
-  </si>
-  <si>
-    <t>Synonyme : genreActivite</t>
+    <t>Le genre identifiant une activité qui nécessite l’application de règles de gestion spécifiques (Synonyme : genreActivite).</t>
   </si>
   <si>
     <t>Liste des genres d'activité</t>
@@ -1393,10 +1369,7 @@
     <t>modeExercice</t>
   </si>
   <si>
-    <t>Le mode d'exercice décrit selon quelle modalité une activité est exercée au regard de l'organisation de la rétribution du professionnel.</t>
-  </si>
-  <si>
-    <t>Synonyme : modeExercice</t>
+    <t>Le mode d'exercice décrit selon quelle modalité une activité est exercée au regard de l'organisation de la rétribution du professionnel (Synonyme : modeExercice).</t>
   </si>
   <si>
     <t>Liste des modes d'exercice</t>
@@ -1411,10 +1384,7 @@
     <t>typeActiviteLiberale</t>
   </si>
   <si>
-    <t>Type d’activité libérale, par exemple: Cabinet; Secteur privé à l'hôpital.</t>
-  </si>
-  <si>
-    <t>Synonyme : typeActiviteLiberale</t>
+    <t>Type d’activité libérale, par exemple: Cabinet; Secteur privé à l'hôpital (Synonyme : typeActiviteLiberale).</t>
   </si>
   <si>
     <t>Liste des types d’activité</t>
@@ -1429,10 +1399,7 @@
     <t>statutProfessionnelSSA</t>
   </si>
   <si>
-    <t>Statut du professionnel du Service de santé des armées.</t>
-  </si>
-  <si>
-    <t>Synonyme : statutProfessionnelSSA</t>
+    <t>Statut du professionnel du Service de santé des armées (Synonyme : statutProfessionnelSSA).</t>
   </si>
   <si>
     <t>Liste des statuts SSA</t>
@@ -1447,10 +1414,7 @@
     <t>statutHospitalier</t>
   </si>
   <si>
-    <t>Statut hospitalier dans le cas d’une activité exercée en établissement public de santé.</t>
-  </si>
-  <si>
-    <t>Synonyme : statutHospitalier</t>
+    <t>Statut hospitalier dans le cas d’une activité exercée en établissement public de santé (Synonyme : statutHospitalier).</t>
   </si>
   <si>
     <t>Liste des statuts hospitaliers</t>
@@ -1465,10 +1429,7 @@
     <t>fonctionR21</t>
   </si>
   <si>
-    <t>Fonction du professionnel au sein de la structure d’exercice.</t>
-  </si>
-  <si>
-    <t>Synonyme : role</t>
+    <t>Fonction du professionnel au sein de la structure d’exercice (Synonyme : role).</t>
   </si>
   <si>
     <t>Liste des fonctions et rôles</t>
@@ -1483,7 +1444,7 @@
     <t>fonctionR96</t>
   </si>
   <si>
-    <t>Autre fonction du domaine sanitaire exercée par le professionnel au sein de la structure d’exercice.</t>
+    <t>Autre fonction du domaine sanitaire exercée par le professionnel au sein de la structure d’exercice (Synonyme : role).</t>
   </si>
   <si>
     <t>PractitionerRole.code.coding:fonctionR85</t>
@@ -1492,7 +1453,7 @@
     <t>fonctionR85</t>
   </si>
   <si>
-    <t>Rôle du professionnel dans la prise en charge des patients ou des usagers.</t>
+    <t>Rôle du professionnel dans la prise en charge des patients ou des usagers (Synonyme : role).</t>
   </si>
   <si>
     <t>Liste des rôles</t>
@@ -1504,10 +1465,7 @@
     <t>metierPharmacienR06</t>
   </si>
   <si>
-    <t>Section du tableau de l’Ordre des pharmaciens (CNOP).</t>
-  </si>
-  <si>
-    <t>Synonyme : sectionOrdrePharmacien</t>
+    <t>Section du tableau de l’Ordre des pharmaciens (CNOP) (Synonyme : sectionOrdrePharmacien).</t>
   </si>
   <si>
     <t>Liste des sections du tableau CNOP</t>
@@ -1522,10 +1480,7 @@
     <t>metierPharmacienG05</t>
   </si>
   <si>
-    <t>Sous-section ou à défaut section du tableau de l’Ordre des pharmaciens (CNOP).</t>
-  </si>
-  <si>
-    <t>Synonyme : sousSectionOrdrePharmacien</t>
+    <t>Sous-section ou à défaut section du tableau de l’Ordre des pharmaciens (CNOP). (Synonyme : sousSectionOrdrePharmacien)</t>
   </si>
   <si>
     <t>Liste des sous-sections du tableau CNOP</t>
@@ -1584,10 +1539,7 @@
     <t>attributionParticuliere</t>
   </si>
   <si>
-    <t>Activité ponctuelle du professionnel de type expertise.</t>
-  </si>
-  <si>
-    <t>Synonyme : attributionParticuliere</t>
+    <t>Activité ponctuelle du professionnel de type expertise (Synonyme : attributionParticuliere).</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J90-AttributionParticuliere-RASS/FHIR/JDV-J90-AttributionParticuliere-RASS</t>
@@ -1599,10 +1551,7 @@
     <t>savoirFaireR38</t>
   </si>
   <si>
-    <t>Spécialité ordinale  reconnue par une autorité d'enregistrement (Ordre ou SSA).</t>
-  </si>
-  <si>
-    <t>Synonyme : specialite</t>
+    <t>Spécialité ordinale  reconnue par une autorité d'enregistrement (Ordre ou SSA) (Synonyme : specialite).</t>
   </si>
   <si>
     <t>Liste des spécialités ordinales</t>
@@ -1617,10 +1566,7 @@
     <t>savoirFaireR39</t>
   </si>
   <si>
-    <t>Compétence acquise par le professionnel.</t>
-  </si>
-  <si>
-    <t>Synonyme : competence</t>
+    <t>Compétence acquise par le professionnel (Synonyme : competence).</t>
   </si>
   <si>
     <t>Liste des compétences</t>
@@ -1632,10 +1578,7 @@
     <t>savoirFaireR40</t>
   </si>
   <si>
-    <t>Compétence exclusive exercée par le professionnel à titre exclusif.</t>
-  </si>
-  <si>
-    <t>Synonyme : competenceExclusive</t>
+    <t>Compétence exclusive exercée par le professionnel à titre exclusif (Synonyme : competenceExclusive).</t>
   </si>
   <si>
     <t>Liste des compétences exclusives</t>
@@ -1647,10 +1590,7 @@
     <t>savoirFaireR42</t>
   </si>
   <si>
-    <t>Diplôme d'études spécialisées complémentaires (DESC).</t>
-  </si>
-  <si>
-    <t>Synonyme : DESCnonQualifian</t>
+    <t>Diplôme d'études spécialisées complémentaires (DESC). Synonyme : DESCnonQualifian</t>
   </si>
   <si>
     <t>Liste des DESC</t>
@@ -1662,10 +1602,7 @@
     <t>savoirFaireR43</t>
   </si>
   <si>
-    <t>Capacité (savoir-faire)d e médecine</t>
-  </si>
-  <si>
-    <t>Synonyme : capaciteSavoirFaire</t>
+    <t>Capacité (savoir-faire)de médecine (Synonyme : capaciteSavoirFaire)</t>
   </si>
   <si>
     <t>Liste des capacités</t>
@@ -1677,10 +1614,7 @@
     <t>savoirFaireR44</t>
   </si>
   <si>
-    <t>Qualification de praticien adjoint contractuel.</t>
-  </si>
-  <si>
-    <t>Synonyme : qualificationPAC</t>
+    <t>Qualification de praticien adjoint contractuel (Synonyme : qualificationPAC).</t>
   </si>
   <si>
     <t>Liste des qualifications</t>
@@ -1692,10 +1626,7 @@
     <t>savoirFaireR45</t>
   </si>
   <si>
-    <t>Fonction qualifiée.</t>
-  </si>
-  <si>
-    <t>Synonyme : fonctionQualifiee</t>
+    <t>Fonction qualifiée (Synonyme : fonctionQualifiee).</t>
   </si>
   <si>
     <t>Liste des fonctions qualifiées</t>
@@ -1707,10 +1638,7 @@
     <t>savoirFaireR97</t>
   </si>
   <si>
-    <t>Droit d'exercice complémentaire.</t>
-  </si>
-  <si>
-    <t>Synonyme : droitExerciceComplementaire</t>
+    <t>Droit d'exercice complémentaire (Synonyme : droitExerciceComplementaire).</t>
   </si>
   <si>
     <t>Liste des droits d'exercice complémentaires</t>
@@ -1722,10 +1650,7 @@
     <t>savoirFaireG13</t>
   </si>
   <si>
-    <t>Orientation particulière.</t>
-  </si>
-  <si>
-    <t>Synonyme : orientationParticuliere</t>
+    <t>Orientation particulière (Synonyme : orientationParticuliere).</t>
   </si>
   <si>
     <t>Liste des orientations particulières</t>
@@ -1737,10 +1662,7 @@
     <t>typeSavoirFaire</t>
   </si>
   <si>
-    <t>Le type de savoir-faire (qualifications/autres attributions).</t>
-  </si>
-  <si>
-    <t>Synonyme : typeSavoirFaire</t>
+    <t>Le type de savoir-faire (qualifications/autres attributions). (Synonyme : typeSavoirFaire)</t>
   </si>
   <si>
     <t>Liste des types de savoir-faire</t>
@@ -1756,13 +1678,10 @@
 </t>
   </si>
   <si>
-    <t>Référence vers la location dans PractitionerRole.contained représentant les coordonnées de l'activité.</t>
+    <t>Référence vers la location dans PractitionerRole.contained représentant les coordonnées de l'activité (idLocation).</t>
   </si>
   <si>
     <t>The location(s) at which this practitioner provides care.</t>
-  </si>
-  <si>
-    <t>idLocation</t>
   </si>
   <si>
     <t>PractitionerRole.healthcareService</t>
@@ -1778,9 +1697,6 @@
     <t>The list of healthcare services that this worker provides for this role's Organization/Location(s).</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>PractitionerRole.telecom</t>
   </si>
   <si>
@@ -1815,10 +1731,7 @@
 </t>
   </si>
   <si>
-    <t>BALs MSS de type PER rattachés à l'identifiant du professionnel de santé  ainsi qu'au lieu de sa situation d'exercice.</t>
-  </si>
-  <si>
-    <t>Synonyme : BoiteLettreMSS</t>
+    <t>BALs MSS de type PER rattachés à l'identifiant du professionnel de santé  ainsi qu'au lieu de sa situation d'exercice (Synonyme : BoiteLettreMSS).</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime</t>
@@ -9576,11 +9489,9 @@
       <c r="M72" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="N72" s="2"/>
+      <c r="O72" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>35</v>
@@ -9646,10 +9557,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9746,10 +9657,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9848,10 +9759,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9877,16 +9788,16 @@
         <v>123</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>35</v>
@@ -9911,31 +9822,31 @@
         <v>35</v>
       </c>
       <c r="X75" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="Y75" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="Y75" t="s" s="2">
+      <c r="Z75" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="Z75" t="s" s="2">
+      <c r="AA75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -9952,10 +9863,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9978,19 +9889,19 @@
         <v>43</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>35</v>
@@ -10018,28 +9929,28 @@
         <v>105</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="Z76" t="s" s="2">
+      <c r="AA76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -10056,10 +9967,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10085,16 +9996,16 @@
         <v>89</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>35</v>
@@ -10107,43 +10018,43 @@
         <v>35</v>
       </c>
       <c r="T77" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
@@ -10160,10 +10071,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10189,13 +10100,13 @@
         <v>56</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10209,43 +10120,43 @@
         <v>35</v>
       </c>
       <c r="T78" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>36</v>
@@ -10262,10 +10173,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10291,13 +10202,13 @@
         <v>230</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10347,7 +10258,7 @@
         <v>35</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>36</v>
@@ -10359,15 +10270,15 @@
         <v>54</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10390,16 +10301,16 @@
         <v>43</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10449,7 +10360,7 @@
         <v>35</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>36</v>
@@ -10461,15 +10372,15 @@
         <v>54</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10492,26 +10403,26 @@
         <v>43</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="O81" t="s" s="2">
+      <c r="P81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q81" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="P81" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q81" t="s" s="2">
-        <v>366</v>
-      </c>
       <c r="R81" t="s" s="2">
         <v>35</v>
       </c>
@@ -10555,7 +10466,7 @@
         <v>35</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>36</v>
@@ -10572,10 +10483,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10601,16 +10512,16 @@
         <v>230</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="O82" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>35</v>
@@ -10659,7 +10570,7 @@
         <v>35</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>36</v>
@@ -10671,15 +10582,15 @@
         <v>54</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10776,10 +10687,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10878,10 +10789,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10907,13 +10818,13 @@
         <v>237</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M85" t="s" s="2">
         <v>239</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10980,10 +10891,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11009,13 +10920,13 @@
         <v>237</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M86" t="s" s="2">
         <v>246</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11084,10 +10995,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11110,16 +11021,16 @@
         <v>43</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11169,7 +11080,7 @@
         <v>35</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>36</v>
@@ -11181,15 +11092,15 @@
         <v>54</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11212,16 +11123,16 @@
         <v>43</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M88" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="N88" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11271,7 +11182,7 @@
         <v>35</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>36</v>
@@ -11283,15 +11194,15 @@
         <v>54</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11314,19 +11225,19 @@
         <v>43</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>35</v>
@@ -11351,13 +11262,13 @@
         <v>35</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>35</v>
@@ -11375,7 +11286,7 @@
         <v>35</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>36</v>
@@ -11392,10 +11303,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11492,10 +11403,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11594,10 +11505,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11623,16 +11534,16 @@
         <v>101</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>35</v>
@@ -11669,7 +11580,7 @@
         <v>35</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AC92" s="2"/>
       <c r="AD92" t="s" s="2">
@@ -11679,7 +11590,7 @@
         <v>68</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>36</v>
@@ -11696,13 +11607,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>35</v>
@@ -11727,16 +11638,16 @@
         <v>101</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="M93" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O93" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>35</v>
@@ -11761,13 +11672,13 @@
         <v>35</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>35</v>
@@ -11785,7 +11696,7 @@
         <v>35</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>36</v>
@@ -11802,13 +11713,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>35</v>
@@ -11833,16 +11744,16 @@
         <v>101</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O94" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>35</v>
@@ -11867,13 +11778,13 @@
         <v>35</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>35</v>
@@ -11891,7 +11802,7 @@
         <v>35</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>36</v>
@@ -11908,13 +11819,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>35</v>
@@ -11939,16 +11850,16 @@
         <v>101</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="M95" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O95" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>35</v>
@@ -11973,13 +11884,13 @@
         <v>35</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>35</v>
@@ -11997,7 +11908,7 @@
         <v>35</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>36</v>
@@ -12014,13 +11925,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>35</v>
@@ -12045,16 +11956,16 @@
         <v>101</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="M96" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O96" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>35</v>
@@ -12079,13 +11990,13 @@
         <v>35</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>35</v>
@@ -12103,7 +12014,7 @@
         <v>35</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>36</v>
@@ -12120,13 +12031,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>35</v>
@@ -12151,16 +12062,16 @@
         <v>101</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="M97" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O97" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>35</v>
@@ -12185,13 +12096,13 @@
         <v>35</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>35</v>
@@ -12209,7 +12120,7 @@
         <v>35</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>36</v>
@@ -12226,13 +12137,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>35</v>
@@ -12257,16 +12168,16 @@
         <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="M98" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O98" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>35</v>
@@ -12291,13 +12202,13 @@
         <v>35</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>35</v>
@@ -12315,7 +12226,7 @@
         <v>35</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>36</v>
@@ -12332,13 +12243,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>35</v>
@@ -12363,16 +12274,16 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="M99" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O99" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>35</v>
@@ -12397,13 +12308,13 @@
         <v>35</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>35</v>
@@ -12421,7 +12332,7 @@
         <v>35</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>36</v>
@@ -12438,13 +12349,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>35</v>
@@ -12469,16 +12380,16 @@
         <v>101</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="M100" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O100" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>35</v>
@@ -12503,13 +12414,13 @@
         <v>35</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>35</v>
@@ -12527,7 +12438,7 @@
         <v>35</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>36</v>
@@ -12544,13 +12455,13 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>35</v>
@@ -12575,16 +12486,16 @@
         <v>101</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="M101" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O101" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>35</v>
@@ -12609,13 +12520,13 @@
         <v>35</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>35</v>
@@ -12633,7 +12544,7 @@
         <v>35</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>36</v>
@@ -12650,13 +12561,13 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>35</v>
@@ -12681,16 +12592,16 @@
         <v>101</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="M102" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O102" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>35</v>
@@ -12715,13 +12626,13 @@
         <v>35</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>35</v>
@@ -12739,7 +12650,7 @@
         <v>35</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>36</v>
@@ -12756,13 +12667,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>35</v>
@@ -12787,16 +12698,16 @@
         <v>101</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="M103" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O103" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>35</v>
@@ -12821,13 +12732,13 @@
         <v>35</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>35</v>
@@ -12845,7 +12756,7 @@
         <v>35</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>36</v>
@@ -12862,13 +12773,13 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>35</v>
@@ -12893,16 +12804,16 @@
         <v>101</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="M104" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>35</v>
@@ -12927,13 +12838,13 @@
         <v>35</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>35</v>
@@ -12951,7 +12862,7 @@
         <v>35</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>36</v>
@@ -12968,13 +12879,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>35</v>
@@ -12999,16 +12910,16 @@
         <v>101</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="M105" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O105" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>35</v>
@@ -13033,13 +12944,13 @@
         <v>35</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>35</v>
@@ -13057,7 +12968,7 @@
         <v>35</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>36</v>
@@ -13074,13 +12985,13 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>35</v>
@@ -13105,16 +13016,16 @@
         <v>101</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="M106" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O106" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>35</v>
@@ -13139,13 +13050,13 @@
         <v>35</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>35</v>
@@ -13163,7 +13074,7 @@
         <v>35</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>36</v>
@@ -13180,13 +13091,13 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>35</v>
@@ -13211,16 +13122,16 @@
         <v>101</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="M107" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>35</v>
@@ -13245,13 +13156,13 @@
         <v>35</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>35</v>
@@ -13269,7 +13180,7 @@
         <v>35</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>36</v>
@@ -13286,10 +13197,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13315,16 +13226,16 @@
         <v>56</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>35</v>
@@ -13373,7 +13284,7 @@
         <v>35</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>36</v>
@@ -13390,10 +13301,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13416,16 +13327,16 @@
         <v>43</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -13451,22 +13362,22 @@
         <v>35</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>35</v>
@@ -13475,7 +13386,7 @@
         <v>68</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>36</v>
@@ -13492,13 +13403,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>35</v>
@@ -13520,16 +13431,16 @@
         <v>43</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13555,11 +13466,11 @@
         <v>35</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y110" s="2"/>
       <c r="Z110" t="s" s="2">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>35</v>
@@ -13577,7 +13488,7 @@
         <v>35</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>36</v>
@@ -13594,13 +13505,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>35</v>
@@ -13622,16 +13533,16 @@
         <v>43</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>509</v>
+        <v>481</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -13657,13 +13568,13 @@
         <v>35</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>35</v>
@@ -13681,7 +13592,7 @@
         <v>35</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>36</v>
@@ -13698,13 +13609,13 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>35</v>
@@ -13726,16 +13637,16 @@
         <v>43</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>515</v>
+        <v>481</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -13761,13 +13672,13 @@
         <v>35</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>35</v>
@@ -13785,7 +13696,7 @@
         <v>35</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>36</v>
@@ -13802,13 +13713,13 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>35</v>
@@ -13830,16 +13741,16 @@
         <v>43</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>520</v>
+        <v>481</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13865,13 +13776,13 @@
         <v>35</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>35</v>
@@ -13889,7 +13800,7 @@
         <v>35</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>36</v>
@@ -13906,13 +13817,13 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>35</v>
@@ -13934,16 +13845,16 @@
         <v>43</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>525</v>
+        <v>481</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13969,13 +13880,13 @@
         <v>35</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>35</v>
@@ -13993,7 +13904,7 @@
         <v>35</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>36</v>
@@ -14010,13 +13921,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>35</v>
@@ -14038,16 +13949,16 @@
         <v>43</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>530</v>
+        <v>481</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14073,13 +13984,13 @@
         <v>35</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>35</v>
@@ -14097,7 +14008,7 @@
         <v>35</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>36</v>
@@ -14114,13 +14025,13 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>35</v>
@@ -14142,16 +14053,16 @@
         <v>43</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>535</v>
+        <v>481</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -14177,13 +14088,13 @@
         <v>35</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>536</v>
+        <v>514</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>35</v>
@@ -14201,7 +14112,7 @@
         <v>35</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>36</v>
@@ -14218,13 +14129,13 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>537</v>
+        <v>515</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>538</v>
+        <v>516</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>35</v>
@@ -14246,16 +14157,16 @@
         <v>43</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>539</v>
+        <v>517</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>540</v>
+        <v>481</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -14281,13 +14192,13 @@
         <v>35</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>35</v>
@@ -14305,7 +14216,7 @@
         <v>35</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>36</v>
@@ -14322,13 +14233,13 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>542</v>
+        <v>519</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>35</v>
@@ -14350,16 +14261,16 @@
         <v>43</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>544</v>
+        <v>521</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>545</v>
+        <v>481</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -14385,13 +14296,13 @@
         <v>35</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>35</v>
@@ -14409,7 +14320,7 @@
         <v>35</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>36</v>
@@ -14426,13 +14337,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>548</v>
+        <v>524</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>35</v>
@@ -14454,16 +14365,16 @@
         <v>43</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>549</v>
+        <v>525</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>550</v>
+        <v>481</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -14489,13 +14400,13 @@
         <v>35</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>551</v>
+        <v>526</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>35</v>
@@ -14513,7 +14424,7 @@
         <v>35</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>36</v>
@@ -14530,13 +14441,13 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>552</v>
+        <v>527</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>553</v>
+        <v>528</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>35</v>
@@ -14558,16 +14469,16 @@
         <v>43</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>554</v>
+        <v>529</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>555</v>
+        <v>481</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -14593,13 +14504,13 @@
         <v>35</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>556</v>
+        <v>530</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>557</v>
+        <v>531</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>35</v>
@@ -14617,7 +14528,7 @@
         <v>35</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>36</v>
@@ -14634,10 +14545,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14660,16 +14571,16 @@
         <v>43</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>559</v>
+        <v>533</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>560</v>
+        <v>534</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>562</v>
+        <v>382</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -14719,7 +14630,7 @@
         <v>35</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>36</v>
@@ -14731,15 +14642,15 @@
         <v>54</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>563</v>
+        <v>536</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>563</v>
+        <v>536</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14762,16 +14673,16 @@
         <v>35</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>564</v>
+        <v>537</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>565</v>
+        <v>538</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>566</v>
+        <v>539</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>567</v>
+        <v>382</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14821,7 +14732,7 @@
         <v>35</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>563</v>
+        <v>536</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>36</v>
@@ -14833,15 +14744,15 @@
         <v>54</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14864,17 +14775,17 @@
         <v>43</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>569</v>
+        <v>541</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>570</v>
+        <v>542</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>571</v>
+        <v>543</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>572</v>
+        <v>544</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>35</v>
@@ -14911,7 +14822,7 @@
         <v>35</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>573</v>
+        <v>545</v>
       </c>
       <c r="AC123" s="2"/>
       <c r="AD123" t="s" s="2">
@@ -14921,7 +14832,7 @@
         <v>68</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>36</v>
@@ -14933,18 +14844,18 @@
         <v>54</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>574</v>
+        <v>546</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>575</v>
+        <v>547</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>576</v>
+        <v>548</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>35</v>
@@ -14966,19 +14877,17 @@
         <v>35</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>577</v>
+        <v>549</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>572</v>
+        <v>544</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>35</v>
@@ -15027,7 +14936,7 @@
         <v>35</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>36</v>
@@ -15039,15 +14948,15 @@
         <v>54</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>574</v>
+        <v>546</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>580</v>
+        <v>551</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>580</v>
+        <v>551</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15070,16 +14979,16 @@
         <v>35</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>581</v>
+        <v>552</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>582</v>
+        <v>553</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>583</v>
+        <v>554</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>584</v>
+        <v>555</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -15129,7 +15038,7 @@
         <v>35</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>580</v>
+        <v>551</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>36</v>
@@ -15146,10 +15055,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>585</v>
+        <v>556</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>585</v>
+        <v>556</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15246,10 +15155,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>586</v>
+        <v>557</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>586</v>
+        <v>557</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15348,14 +15257,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>587</v>
+        <v>558</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>587</v>
+        <v>558</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>588</v>
+        <v>559</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -15377,10 +15286,10 @@
         <v>62</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>589</v>
+        <v>560</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>590</v>
+        <v>561</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>65</v>
@@ -15435,7 +15344,7 @@
         <v>35</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>591</v>
+        <v>562</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>36</v>
@@ -15452,10 +15361,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>592</v>
+        <v>563</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>592</v>
+        <v>563</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15481,13 +15390,13 @@
         <v>123</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>594</v>
+        <v>565</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>595</v>
+        <v>566</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -15513,13 +15422,13 @@
         <v>35</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>596</v>
+        <v>567</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>597</v>
+        <v>568</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>35</v>
@@ -15537,7 +15446,7 @@
         <v>35</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>592</v>
+        <v>563</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>36</v>
@@ -15554,10 +15463,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>598</v>
+        <v>569</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>598</v>
+        <v>569</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15580,13 +15489,13 @@
         <v>35</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>599</v>
+        <v>570</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>600</v>
+        <v>571</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -15637,7 +15546,7 @@
         <v>35</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>598</v>
+        <v>569</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>36</v>
@@ -15654,10 +15563,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>601</v>
+        <v>572</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>601</v>
+        <v>572</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15680,16 +15589,16 @@
         <v>35</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>602</v>
+        <v>573</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>603</v>
+        <v>574</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>604</v>
+        <v>575</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -15739,7 +15648,7 @@
         <v>35</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>601</v>
+        <v>572</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>36</v>
@@ -15756,10 +15665,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>606</v>
+        <v>577</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>606</v>
+        <v>577</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15782,16 +15691,16 @@
         <v>35</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>602</v>
+        <v>573</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>607</v>
+        <v>578</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>608</v>
+        <v>579</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -15841,7 +15750,7 @@
         <v>35</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>606</v>
+        <v>577</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>36</v>
@@ -15858,10 +15767,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15884,13 +15793,13 @@
         <v>35</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L133" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="M133" t="s" s="2">
-        <v>611</v>
+        <v>582</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15941,7 +15850,7 @@
         <v>35</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>36</v>
@@ -15958,10 +15867,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>612</v>
+        <v>583</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>612</v>
+        <v>583</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16058,10 +15967,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>613</v>
+        <v>584</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>613</v>
+        <v>584</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16160,14 +16069,14 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>614</v>
+        <v>585</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>614</v>
+        <v>585</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>588</v>
+        <v>559</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -16189,10 +16098,10 @@
         <v>62</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>589</v>
+        <v>560</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>590</v>
+        <v>561</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>65</v>
@@ -16247,7 +16156,7 @@
         <v>35</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>591</v>
+        <v>562</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>36</v>
@@ -16264,10 +16173,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>615</v>
+        <v>586</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>615</v>
+        <v>586</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16293,13 +16202,13 @@
         <v>56</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>616</v>
+        <v>587</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>617</v>
+        <v>588</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>595</v>
+        <v>566</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -16349,7 +16258,7 @@
         <v>35</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>615</v>
+        <v>586</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>42</v>
@@ -16366,10 +16275,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>618</v>
+        <v>589</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>618</v>
+        <v>589</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16395,13 +16304,13 @@
         <v>230</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>619</v>
+        <v>590</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>620</v>
+        <v>591</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -16451,7 +16360,7 @@
         <v>35</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>618</v>
+        <v>589</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>36</v>
@@ -16463,15 +16372,15 @@
         <v>54</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>621</v>
+        <v>592</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>621</v>
+        <v>592</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16497,13 +16406,13 @@
         <v>56</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>622</v>
+        <v>593</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>623</v>
+        <v>594</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>595</v>
+        <v>566</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -16553,7 +16462,7 @@
         <v>35</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>621</v>
+        <v>592</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>36</v>
@@ -16570,10 +16479,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>624</v>
+        <v>595</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>624</v>
+        <v>595</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16596,19 +16505,19 @@
         <v>35</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>625</v>
+        <v>596</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>626</v>
+        <v>597</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>627</v>
+        <v>598</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>567</v>
+        <v>382</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>628</v>
+        <v>599</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>35</v>
@@ -16657,7 +16566,7 @@
         <v>35</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>624</v>
+        <v>595</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>36</v>
@@ -16669,7 +16578,7 @@
         <v>54</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-10T14:51:06+00:00</t>
+    <t>2023-07-11T12:08:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:23:29+00:00</t>
+    <t>2023-12-18T12:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:24:31+00:00</t>
+    <t>2023-12-18T13:29:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T13:29:44+00:00</t>
+    <t>2023-12-19T08:36:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-2</t>
+    <t>1.0.0-ballot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T08:36:38+00:00</t>
+    <t>2023-12-19T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T15:11:46+00:00</t>
+    <t>2023-12-21T16:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:59:47+00:00</t>
+    <t>2024-01-11T15:09:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T15:09:13+00:00</t>
+    <t>2024-02-05T18:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:24+00:00</t>
+    <t>2024-02-05T18:22:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:48+00:00</t>
+    <t>2024-02-05T18:23:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:23:38+00:00</t>
+    <t>2024-02-07T08:22:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T08:22:38+00:00</t>
+    <t>2024-02-08T15:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:43:07+00:00</t>
+    <t>2024-02-08T15:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:45:12+00:00</t>
+    <t>2024-02-16T10:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:46:50+00:00</t>
+    <t>2024-02-16T10:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:57:00+00:00</t>
+    <t>2024-02-16T18:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8642,7 +8642,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
